--- a/data/trans_orig/P70C3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023</t>
+          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155388</t>
+          <t>155752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>197524</t>
+          <t>193691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117864</t>
+          <t>117843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145226</t>
+          <t>144716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>283487</t>
+          <t>282216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>331461</t>
+          <t>329899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60027</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89679</t>
+          <t>92080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60993</t>
+          <t>58926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84635</t>
+          <t>83434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126778</t>
+          <t>128359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166840</t>
+          <t>164813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>19748</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>40258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27945</t>
+          <t>27284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37079</t>
+          <t>36344</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63836</t>
+          <t>62596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>23970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48012</t>
+          <t>50886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>38488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66579</t>
+          <t>68788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19507</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44382</t>
+          <t>45482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17791</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386939</t>
+          <t>391104</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679555</t>
+          <t>688912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183750</t>
+          <t>181120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219416</t>
+          <t>217106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592586</t>
+          <t>589597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>985686</t>
+          <t>939468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54414</t>
+          <t>56398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200052</t>
+          <t>200924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>101548</t>
+          <t>102630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132081</t>
+          <t>134657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121175</t>
+          <t>134446</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>318255</t>
+          <t>323349</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23959</t>
+          <t>25274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99627</t>
+          <t>99831</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46392</t>
+          <t>45500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46092</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131517</t>
+          <t>133202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77222</t>
+          <t>78587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43473</t>
+          <t>42323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>39172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110068</t>
+          <t>111173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50386</t>
+          <t>52923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20575</t>
+          <t>20240</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21339</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63557</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>214641</t>
+          <t>213022</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>256238</t>
+          <t>255310</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187070</t>
+          <t>187062</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>242477</t>
+          <t>245804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>416025</t>
+          <t>413030</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>482873</t>
+          <t>480096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47297</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81604</t>
+          <t>82137</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41532</t>
+          <t>41365</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76883</t>
+          <t>76554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99639</t>
+          <t>99678</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146233</t>
+          <t>147575</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43076</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14154</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69148</t>
+          <t>70809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38248</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58986</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>322</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>260299</t>
+          <t>260591</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>305091</t>
+          <t>303231</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264645</t>
+          <t>265581</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>366425</t>
+          <t>374946</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>543510</t>
+          <t>543459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>665420</t>
+          <t>671382</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103772</t>
+          <t>103988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>142943</t>
+          <t>144515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63870</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123425</t>
+          <t>123487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>174877</t>
+          <t>169909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>256753</t>
+          <t>253589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35801</t>
+          <t>34954</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38181</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37273</t>
+          <t>37808</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>66169</t>
+          <t>65829</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30557</t>
+          <t>30620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>49372</t>
+          <t>48705</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25224</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>43816</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19061</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33820</t>
+          <t>37209</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45217</t>
+          <t>46475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1100609</t>
+          <t>1096775</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1464224</t>
+          <t>1490859</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>787801</t>
+          <t>793114</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>948443</t>
+          <t>932006</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1918805</t>
+          <t>1914075</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2339860</t>
+          <t>2376111</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>246621</t>
+          <t>246584</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>459577</t>
+          <t>459871</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>293351</t>
+          <t>295082</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>384547</t>
+          <t>382589</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>588144</t>
+          <t>570082</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>826312</t>
+          <t>827734</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>97115</t>
+          <t>94785</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>176428</t>
+          <t>176221</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>87040</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>128919</t>
+          <t>125268</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>199122</t>
+          <t>190239</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>289608</t>
+          <t>286151</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>79429</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>154573</t>
+          <t>152722</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>72518</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>107340</t>
+          <t>106799</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>167488</t>
+          <t>159040</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>245454</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40309</t>
+          <t>37659</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>84900</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38448</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>66176</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>88447</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>139554</t>
+          <t>141313</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>44316</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>48413</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>76903</t>
+          <t>77691</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>174967</t>
+          <t>199371</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155752</t>
+          <t>177504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>193691</t>
+          <t>218657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>131318</t>
+          <t>145222</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117843</t>
+          <t>130564</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144716</t>
+          <t>160223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>306284</t>
+          <t>344593</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>282216</t>
+          <t>315637</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>329899</t>
+          <t>369455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -838,67 +838,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>80384</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60330</t>
+          <t>65819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92080</t>
+          <t>99442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>76421</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64022</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>90800</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>27,54%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71422</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58926</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83434</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>145615</t>
+          <t>156805</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128359</t>
+          <t>137377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164813</t>
+          <t>177372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28556</t>
+          <t>29440</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40258</t>
+          <t>43297</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>49982</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>37413</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>64500</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>48394</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>36344</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>62596</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34507</t>
+          <t>35891</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50886</t>
+          <t>53128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>50706</t>
+          <t>52320</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38488</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68788</t>
+          <t>71749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>30839</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19271</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18615</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>334309</t>
+          <t>368115</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>334309</t>
+          <t>368115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>334309</t>
+          <t>368115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>256216</t>
+          <t>277540</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>256216</t>
+          <t>277540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256216</t>
+          <t>277540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>590525</t>
+          <t>645655</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>590525</t>
+          <t>645655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>590525</t>
+          <t>645655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526755</t>
+          <t>318212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>391104</t>
+          <t>290468</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>688912</t>
+          <t>347240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>201057</t>
+          <t>224643</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181120</t>
+          <t>204836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217106</t>
+          <t>243856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>727812</t>
+          <t>542854</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>589597</t>
+          <t>509161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>939468</t>
+          <t>577128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>129874</t>
+          <t>151022</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56398</t>
+          <t>127567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200924</t>
+          <t>175837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>116427</t>
+          <t>128830</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>102630</t>
+          <t>111896</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134657</t>
+          <t>146104</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>246300</t>
+          <t>279851</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134446</t>
+          <t>252783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>323349</t>
+          <t>312159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62150</t>
+          <t>64789</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>49317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99831</t>
+          <t>85665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35267</t>
+          <t>38395</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45500</t>
+          <t>50557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>97417</t>
+          <t>103184</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51946</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133202</t>
+          <t>125071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48031</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>35971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78587</t>
+          <t>69237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32734</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>27358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42323</t>
+          <t>48797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>80765</t>
+          <t>88790</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39172</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111173</t>
+          <t>110970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>49146</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>44774</t>
+          <t>49896</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>37382</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64607</t>
+          <t>66347</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>24752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>806332</t>
+          <t>628627</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>806332</t>
+          <t>628627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>806332</t>
+          <t>628627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>450606</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>450606</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>450606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1209157</t>
+          <t>1079233</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1209157</t>
+          <t>1079233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1209157</t>
+          <t>1079233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>235911</t>
+          <t>272794</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>213022</t>
+          <t>249259</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>255310</t>
+          <t>295769</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207441</t>
+          <t>204172</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187062</t>
+          <t>185819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>245804</t>
+          <t>220004</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>443352</t>
+          <t>476966</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>413030</t>
+          <t>449081</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>480096</t>
+          <t>505716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>62768</t>
+          <t>81184</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82137</t>
+          <t>101118</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61575</t>
+          <t>73434</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41365</t>
+          <t>60458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76554</t>
+          <t>88983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>124343</t>
+          <t>154618</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99678</t>
+          <t>131552</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147575</t>
+          <t>182351</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>27371</t>
+          <t>31688</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>18253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33989</t>
+          <t>36183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>51221</t>
+          <t>57576</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>44013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70809</t>
+          <t>77103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25038</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38202</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>20667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>43097</t>
+          <t>46897</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30507</t>
+          <t>32838</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>60190</t>
+          <t>63529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,67 +2915,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>10543</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>5299</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>20593</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>8168</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3935</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>15310</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>323590</t>
+          <t>338612</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>323590</t>
+          <t>338612</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>323590</t>
+          <t>338612</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>680958</t>
+          <t>760209</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>680958</t>
+          <t>760209</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>680958</t>
+          <t>760209</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>283084</t>
+          <t>305907</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>260591</t>
+          <t>280223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>303231</t>
+          <t>328240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>301619</t>
+          <t>254065</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>265581</t>
+          <t>235365</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>374946</t>
+          <t>271523</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>584703</t>
+          <t>559972</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>543459</t>
+          <t>528044</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>671382</t>
+          <t>589278</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>123678</t>
+          <t>135157</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103988</t>
+          <t>115004</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144515</t>
+          <t>155483</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100304</t>
+          <t>110334</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59052</t>
+          <t>95980</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123487</t>
+          <t>127923</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>223982</t>
+          <t>245491</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>169909</t>
+          <t>219443</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253589</t>
+          <t>273132</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24246</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16372</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34954</t>
+          <t>49004</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27536</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>37467</t>
+          <t>43752</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>51782</t>
+          <t>66759</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>52359</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>65829</t>
+          <t>86018</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30620</t>
+          <t>30846</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>36651</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48705</t>
+          <t>49065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15691</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>26495</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>30737</t>
+          <t>34141</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43816</t>
+          <t>45241</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>17615</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>32764</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>472203</t>
+          <t>517861</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>480858</t>
+          <t>448926</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>480858</t>
+          <t>448926</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>480858</t>
+          <t>448926</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>953061</t>
+          <t>966787</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>953061</t>
+          <t>966787</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>953061</t>
+          <t>966787</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1220717</t>
+          <t>1096283</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1096775</t>
+          <t>1043277</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1490859</t>
+          <t>1143020</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>841435</t>
+          <t>828102</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>793114</t>
+          <t>794624</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>932006</t>
+          <t>863214</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2062152</t>
+          <t>1924384</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1914075</t>
+          <t>1855821</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2376111</t>
+          <t>1985658</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>390512</t>
+          <t>447746</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>246584</t>
+          <t>410939</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>459871</t>
+          <t>489286</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>349728</t>
+          <t>389018</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>295082</t>
+          <t>359376</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>382589</t>
+          <t>422537</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>740240</t>
+          <t>836764</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>570082</t>
+          <t>785447</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>827734</t>
+          <t>885705</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>142323</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>133456</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>176221</t>
+          <t>188963</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>118216</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>87040</t>
+          <t>100326</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>125268</t>
+          <t>137841</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>248813</t>
+          <t>277500</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>190239</t>
+          <t>245777</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>286151</t>
+          <t>311375</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>123297</t>
+          <t>129543</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>106890</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>152722</t>
+          <t>156416</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>87922</t>
+          <t>96593</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>80090</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>106799</t>
+          <t>114341</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>211219</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>159040</t>
+          <t>197936</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>245454</t>
+          <t>260345</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>89230</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>51755</t>
+          <t>60954</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>66176</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>114840</t>
+          <t>128485</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>88447</t>
+          <t>108059</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>141313</t>
+          <t>155142</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>50953</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>31673</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>58613</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>77691</t>
+          <t>76991</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
